--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
@@ -2137,7 +2137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:42</t>
+    <t xml:space="preserve">2026-09-07 12:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2018.xlsx
@@ -2137,7 +2137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:49</t>
+    <t xml:space="preserve">2026-09-08 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
